--- a/excel/sablonlar/ayo_cost_excel.xlsx
+++ b/excel/sablonlar/ayo_cost_excel.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\socket\excel\sablonlar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69F25A6-1469-476B-A68A-F34E97949149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BE239F-2929-4735-8837-CEFD23F5C0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="creditcard" sheetId="1" r:id="rId1"/>
     <sheet name="travel" sheetId="3" r:id="rId2"/>
     <sheet name="wage" sheetId="4" r:id="rId3"/>
     <sheet name="sample" sheetId="5" r:id="rId4"/>
-    <sheet name="other" sheetId="6" r:id="rId5"/>
+    <sheet name="fuil" sheetId="6" r:id="rId5"/>
+    <sheet name="meal" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="5">
   <si>
     <t>MONTH</t>
   </si>
@@ -950,4 +951,108 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E279D72-EE53-4961-965F-D13CA5E309DF}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>